--- a/condtional (if,ifs,logical.xlsx
+++ b/condtional (if,ifs,logical.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/44ebe243d3ac746e/Desktop/Dmart_sales_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B035715-87DF-4AAD-957F-9A1F88BA7AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{0B035715-87DF-4AAD-957F-9A1F88BA7AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7D34FA7-FD1F-4CDD-B186-4D252B6FABE5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0CA0669F-5B2A-4576-8E77-FDEAA39EF5CF}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>if error</t>
+  </si>
+  <si>
+    <t>Nested if</t>
   </si>
 </sst>
 </file>
@@ -171,7 +174,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="15">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -190,6 +193,34 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -211,30 +242,6 @@
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -248,35 +255,42 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{658514AB-8F46-49A4-90E9-CF8E6FF92F72}" name="Table1" displayName="Table1" ref="C2:N8" totalsRowShown="0" headerRowDxfId="5" dataDxfId="6">
-  <autoFilter ref="C2:N8" xr:uid="{658514AB-8F46-49A4-90E9-CF8E6FF92F72}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{168CAAF9-AE00-4AC7-9FFE-5FCBB1BE8FD4}" name="Roll No" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{49E91D08-700D-4B37-91B2-A3E21528861C}" name="Name" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{1EE082AA-71FB-48D1-948B-059FDA52771B}" name="Marathi" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{5457DD40-748B-44AB-BE9A-D1CB856E36EA}" name="English" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{9DD98CDC-69AC-41D8-96E5-90BC44D2E2ED}" name="Science " dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{FDE6E507-93A9-4594-91B5-B6E7F77F2DCC}" name="Total" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{658514AB-8F46-49A4-90E9-CF8E6FF92F72}" name="Table1" displayName="Table1" ref="C2:O8" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+  <autoFilter ref="C2:O8" xr:uid="{658514AB-8F46-49A4-90E9-CF8E6FF92F72}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{168CAAF9-AE00-4AC7-9FFE-5FCBB1BE8FD4}" name="Roll No" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{49E91D08-700D-4B37-91B2-A3E21528861C}" name="Name" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{1EE082AA-71FB-48D1-948B-059FDA52771B}" name="Marathi" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{5457DD40-748B-44AB-BE9A-D1CB856E36EA}" name="English" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{9DD98CDC-69AC-41D8-96E5-90BC44D2E2ED}" name="Science " dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{FDE6E507-93A9-4594-91B5-B6E7F77F2DCC}" name="Total" dataDxfId="7">
       <calculatedColumnFormula>E3+F3+G3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6452DE4F-54CB-46F4-9D67-C0C88D870F27}" name="Remark" dataDxfId="7">
+    <tableColumn id="7" xr3:uid="{6452DE4F-54CB-46F4-9D67-C0C88D870F27}" name="Remark" dataDxfId="6">
       <calculatedColumnFormula>IF(H3&gt;200,"good","bad")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{E4EAED23-2039-4A3A-96F1-841718101481}" name="Ifs" dataDxfId="4">
+    <tableColumn id="8" xr3:uid="{E4EAED23-2039-4A3A-96F1-841718101481}" name="Ifs" dataDxfId="5">
       <calculatedColumnFormula array="1">_xlfn.IFS(H3&lt;180,"Bad Marks",H3&lt;230,"Average Marks",H3&gt;250,"Good Marks")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{0D1EE5E1-4B53-4F12-9FB3-28B194B88EC9}" name="And" dataDxfId="3">
+    <tableColumn id="9" xr3:uid="{0D1EE5E1-4B53-4F12-9FB3-28B194B88EC9}" name="And" dataDxfId="4">
       <calculatedColumnFormula>AND(G3&lt;100,F3&lt;100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{129B271A-F897-49F4-A8BD-0384B119AABD}" name="Or" dataDxfId="1">
+    <tableColumn id="10" xr3:uid="{129B271A-F897-49F4-A8BD-0384B119AABD}" name="Or" dataDxfId="3">
       <calculatedColumnFormula>OR(G3&lt;250,Table1[[#This Row],[Name]]="Siddhant Chikate")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{59F0665C-9192-49AA-B79D-FA68C92B0962}" name="Not" dataDxfId="2">
       <calculatedColumnFormula>NOT(AND(Table1[[#This Row],[Science ]]&lt;100,Table1[[#This Row],[English]]&lt;100))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{86183AE1-597D-4BE3-8AA1-757501D678F4}" name="if error" dataDxfId="0">
+    <tableColumn id="12" xr3:uid="{86183AE1-597D-4BE3-8AA1-757501D678F4}" name="if error" dataDxfId="1">
       <calculatedColumnFormula array="1">IFERROR(_xlfn.IFS(G3&gt;100,"good marks",F3&gt;50,"average marks"),"something is wrong")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{4311DBA3-C280-4FA8-938D-785909BE3B51}" name="Nested if" dataDxfId="0">
+      <calculatedColumnFormula>IF(Table1[[#This Row],[Science ]]&gt;50,"good ",IF(Table1[[#This Row],[Science ]]&gt;50,))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -580,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E805EB8-995F-41B4-8B7D-6B90CFBC9819}">
-  <dimension ref="C2:N8"/>
+  <dimension ref="C2:O8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="19.6640625" customWidth="1"/>
@@ -590,11 +604,13 @@
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="25.21875" customWidth="1"/>
-    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="8.88671875" customWidth="1"/>
+    <col min="13" max="13" width="8.5546875" customWidth="1"/>
     <col min="14" max="14" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
@@ -631,8 +647,11 @@
       <c r="N2" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="O2" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C3" s="2">
         <v>1</v>
       </c>
@@ -655,10 +674,7 @@
         <f>IF(H3&gt;200,"good","bad")</f>
         <v>good</v>
       </c>
-      <c r="J3" s="2" t="str" cm="1">
-        <f t="array" ref="J3">_xlfn.IFS(H3&lt;180,"Bad Marks",H3&lt;230,"Average Marks",H3&gt;250,"Good Marks")</f>
-        <v>Good Marks</v>
-      </c>
+      <c r="J3" s="2"/>
       <c r="K3" s="2" t="b">
         <f>AND(G3&lt;100,F3&lt;100)</f>
         <v>1</v>
@@ -675,8 +691,12 @@
         <f t="array" ref="N3">IFERROR(_xlfn.IFS(G3&gt;100,"good marks",F3&gt;50,"average marks"),"something is wrong")</f>
         <v>average marks</v>
       </c>
+      <c r="O3" s="3" t="str">
+        <f>IF(Table1[[#This Row],[Science ]]&gt;50,"good ",IF(Table1[[#This Row],[Science ]]&gt;50,))</f>
+        <v xml:space="preserve">good </v>
+      </c>
     </row>
-    <row r="4" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C4" s="2">
         <v>2</v>
       </c>
@@ -690,7 +710,7 @@
         <v>76</v>
       </c>
       <c r="G4" s="2">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="H4" s="2">
         <v>256</v>
@@ -704,7 +724,7 @@
         <v>Good Marks</v>
       </c>
       <c r="K4" s="2" t="b">
-        <f t="shared" ref="K3:K8" si="1">AND(G4&lt;100,F4&lt;100)</f>
+        <f t="shared" ref="K4:K8" si="1">AND(G4&lt;100,F4&lt;100)</f>
         <v>1</v>
       </c>
       <c r="L4" s="2" t="b">
@@ -719,8 +739,12 @@
         <f t="array" ref="N4">IFERROR(_xlfn.IFS(G4&gt;100,"good marks",F4&gt;50,"average marks"),"something is wrong")</f>
         <v>average marks</v>
       </c>
+      <c r="O4" s="3" t="str">
+        <f>IF(Table1[[#This Row],[Science ]]&gt;50,"good ",IF(Table1[[#This Row],[Science ]]&gt;50,))</f>
+        <v xml:space="preserve">good </v>
+      </c>
     </row>
-    <row r="5" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C5" s="2">
         <v>3</v>
       </c>
@@ -763,8 +787,12 @@
         <f t="array" ref="N5">IFERROR(_xlfn.IFS(G5&gt;100,"good marks",F5&gt;50,"average marks"),"something is wrong")</f>
         <v>average marks</v>
       </c>
+      <c r="O5" s="3" t="str">
+        <f>IF(Table1[[#This Row],[Science ]]&gt;50,"good ",IF(Table1[[#This Row],[Science ]]&gt;50,))</f>
+        <v xml:space="preserve">good </v>
+      </c>
     </row>
-    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C6" s="2">
         <v>4</v>
       </c>
@@ -781,7 +809,7 @@
         <v>77</v>
       </c>
       <c r="H6" s="2">
-        <f t="shared" ref="H4:H8" si="2">E6+F6+G6</f>
+        <f t="shared" ref="H6:H8" si="2">E6+F6+G6</f>
         <v>167</v>
       </c>
       <c r="I6" s="2" t="str">
@@ -808,8 +836,12 @@
         <f t="array" ref="N6">IFERROR(_xlfn.IFS(G6&gt;100,"good marks",F6&gt;50,"average marks"),"something is wrong")</f>
         <v>something is wrong</v>
       </c>
+      <c r="O6" s="3" t="str">
+        <f>IF(Table1[[#This Row],[Science ]]&gt;50,"good ",IF(Table1[[#This Row],[Science ]]&gt;50,))</f>
+        <v xml:space="preserve">good </v>
+      </c>
     </row>
-    <row r="7" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C7" s="2">
         <v>5</v>
       </c>
@@ -853,8 +885,12 @@
         <f t="array" ref="N7">IFERROR(_xlfn.IFS(G7&gt;100,"good marks",F7&gt;50,"average marks"),"something is wrong")</f>
         <v>average marks</v>
       </c>
+      <c r="O7" s="3" t="str">
+        <f>IF(Table1[[#This Row],[Science ]]&gt;50,"good ",IF(Table1[[#This Row],[Science ]]&gt;50,))</f>
+        <v xml:space="preserve">good </v>
+      </c>
     </row>
-    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C8" s="2">
         <v>6</v>
       </c>
@@ -897,6 +933,10 @@
       <c r="N8" s="3" t="str" cm="1">
         <f t="array" ref="N8">IFERROR(_xlfn.IFS(G8&gt;100,"good marks",F8&gt;50,"average marks"),"something is wrong")</f>
         <v>average marks</v>
+      </c>
+      <c r="O8" s="3" t="str">
+        <f>IF(Table1[[#This Row],[Science ]]&gt;50,"good ",IF(Table1[[#This Row],[Science ]]&gt;50,))</f>
+        <v xml:space="preserve">good </v>
       </c>
     </row>
   </sheetData>
